--- a/Conversion Script/Set_filter_file_Europe2060.xlsx
+++ b/Conversion Script/Set_filter_file_Europe2060.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nim\Documents\GENeSYS_MOD.data\Conversion Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F78260A-3A18-4A71-B8DD-E71A5BDE3075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F45B71-230E-4A04-8CCA-C574DE0FEEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{0B764928-35F8-4A30-ADCD-C0369050184D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" activeTab="3" xr2:uid="{0B764928-35F8-4A30-ADCD-C0369050184D}"/>
   </bookViews>
   <sheets>
     <sheet name="Region_selection" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="Fuels">#REF!</definedName>
     <definedName name="Technologies">#REF!:B</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2937,7 +2937,7 @@
         <v>124</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -2945,7 +2945,7 @@
         <v>125</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3175,7 +3175,7 @@
         <v>162</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3183,7 +3183,7 @@
         <v>163</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">

--- a/Conversion Script/Set_filter_file_Europe2060.xlsx
+++ b/Conversion Script/Set_filter_file_Europe2060.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nim\Documents\GENeSYS_MOD.data\Conversion Script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F45B71-230E-4A04-8CCA-C574DE0FEEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64880424-B2F2-48B6-909A-21B6FC157E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" activeTab="3" xr2:uid="{0B764928-35F8-4A30-ADCD-C0369050184D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{0B764928-35F8-4A30-ADCD-C0369050184D}"/>
   </bookViews>
   <sheets>
     <sheet name="Region_selection" sheetId="1" r:id="rId1"/>
@@ -3175,7 +3175,7 @@
         <v>162</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3183,7 +3183,7 @@
         <v>163</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
